--- a/output/walk_forward_reports/robust_strategies.xlsx
+++ b/output/walk_forward_reports/robust_strategies.xlsx
@@ -55,6 +55,9 @@
     <t>equal</t>
   </si>
   <si>
+    <t>mvo</t>
+  </si>
+  <si>
     <t>factor_score</t>
   </si>
   <si>
@@ -64,37 +67,34 @@
     <t>min_variance</t>
   </si>
   <si>
-    <t>mvo</t>
-  </si>
-  <si>
-    <t>equal_5G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top1_P20d</t>
+    <t>equal_5G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top3_P30d</t>
   </si>
 </sst>
 </file>
@@ -472,10 +472,10 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -483,11 +483,26 @@
       <c r="E2" t="s">
         <v>17</v>
       </c>
+      <c r="F2">
+        <v>1.757197360578506</v>
+      </c>
+      <c r="G2">
+        <v>1.669588725298132</v>
+      </c>
+      <c r="H2">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I2">
+        <v>0.2406217448324305</v>
+      </c>
+      <c r="J2">
+        <v>-0.05634151683644142</v>
+      </c>
       <c r="K2">
         <v>12</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.09025580481561</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -495,45 +510,75 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
+      <c r="F3">
+        <v>1.767907960155299</v>
+      </c>
+      <c r="G3">
+        <v>2.015456413553579</v>
+      </c>
+      <c r="H3">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I3">
+        <v>0.2905291210833909</v>
+      </c>
+      <c r="J3">
+        <v>-0.04423047170758487</v>
+      </c>
       <c r="K3">
         <v>12</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.056650611123439</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
+      <c r="F4">
+        <v>1.686393291884191</v>
+      </c>
+      <c r="G4">
+        <v>1.937270247711216</v>
+      </c>
+      <c r="H4">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I4">
+        <v>0.3623414427804155</v>
+      </c>
+      <c r="J4">
+        <v>-0.06138795555735376</v>
+      </c>
       <c r="K4">
         <v>12</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.051692964719255</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -541,22 +586,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
+      <c r="F5">
+        <v>1.659298582350115</v>
+      </c>
+      <c r="G5">
+        <v>1.83277528816951</v>
+      </c>
+      <c r="H5">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I5">
+        <v>0.2345236259747293</v>
+      </c>
+      <c r="J5">
+        <v>-0.05966065414100232</v>
+      </c>
       <c r="K5">
         <v>12</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.04462264427237</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -564,22 +624,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
       </c>
+      <c r="F6">
+        <v>1.71400434264802</v>
+      </c>
+      <c r="G6">
+        <v>2.219769667084713</v>
+      </c>
+      <c r="H6">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I6">
+        <v>0.318767977568464</v>
+      </c>
+      <c r="J6">
+        <v>-0.04896836312506155</v>
+      </c>
       <c r="K6">
         <v>12</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.02877610386776</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -587,10 +662,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
@@ -598,11 +673,26 @@
       <c r="E7" t="s">
         <v>22</v>
       </c>
+      <c r="F7">
+        <v>1.768731826515696</v>
+      </c>
+      <c r="G7">
+        <v>2.201755703204457</v>
+      </c>
+      <c r="H7">
+        <v>0.75</v>
+      </c>
+      <c r="I7">
+        <v>0.3183067896086119</v>
+      </c>
+      <c r="J7">
+        <v>-0.04465996781107093</v>
+      </c>
       <c r="K7">
         <v>12</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.026191322194558</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -610,22 +700,37 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
       </c>
+      <c r="F8">
+        <v>1.768731826515696</v>
+      </c>
+      <c r="G8">
+        <v>2.201755703204457</v>
+      </c>
+      <c r="H8">
+        <v>0.75</v>
+      </c>
+      <c r="I8">
+        <v>0.3183067896086119</v>
+      </c>
+      <c r="J8">
+        <v>-0.04465996781107093</v>
+      </c>
       <c r="K8">
         <v>12</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.026191322194558</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -633,22 +738,37 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
       </c>
+      <c r="F9">
+        <v>1.768731826515696</v>
+      </c>
+      <c r="G9">
+        <v>2.201755703204457</v>
+      </c>
+      <c r="H9">
+        <v>0.75</v>
+      </c>
+      <c r="I9">
+        <v>0.3183067896086119</v>
+      </c>
+      <c r="J9">
+        <v>-0.04465996781107093</v>
+      </c>
       <c r="K9">
         <v>12</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.026191322194558</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -656,45 +776,75 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
         <v>25</v>
       </c>
+      <c r="F10">
+        <v>1.768731826515696</v>
+      </c>
+      <c r="G10">
+        <v>2.201755703204457</v>
+      </c>
+      <c r="H10">
+        <v>0.75</v>
+      </c>
+      <c r="I10">
+        <v>0.3183067896086119</v>
+      </c>
+      <c r="J10">
+        <v>-0.04465996781107093</v>
+      </c>
       <c r="K10">
         <v>12</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.026191322194558</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
       </c>
+      <c r="F11">
+        <v>1.567441294999911</v>
+      </c>
+      <c r="G11">
+        <v>1.730542442322888</v>
+      </c>
+      <c r="H11">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="I11">
+        <v>0.3550876528382974</v>
+      </c>
+      <c r="J11">
+        <v>-0.05553894485150641</v>
+      </c>
       <c r="K11">
         <v>12</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>0.9868447974121637</v>
       </c>
     </row>
   </sheetData>
